--- a/src/test/resources/TestData_folder/SwagLabsUserInfo.xlsx
+++ b/src/test/resources/TestData_folder/SwagLabsUserInfo.xlsx
@@ -98,12 +98,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -114,7 +129,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>

--- a/src/test/resources/TestData_folder/SwagLabsUserInfo.xlsx
+++ b/src/test/resources/TestData_folder/SwagLabsUserInfo.xlsx
@@ -3,20 +3,20 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="164011"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\NewSeleniumWorkspace\Selenium_M9\src\test\resources\TestData_folder\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7500"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7500" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="LogInCredentials" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="11">
   <si>
     <t>UserName</t>
   </si>
@@ -51,12 +51,19 @@
   </si>
   <si>
     <t>visual_user</t>
+  </si>
+  <si>
+    <t>NewValue1</t>
+  </si>
+  <si>
+    <t>NewValue2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="0"/>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -415,8 +422,8 @@
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="24.5703125"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="13.85546875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
